--- a/documents/Group06_Project Contribution.xlsx
+++ b/documents/Group06_Project Contribution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DS-Visualizer-Group-6\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0641FA3F-49CF-485A-BBF5-1C4A0C05EB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7319B32F-8232-4D69-9C39-F6FF5C45494A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -680,7 +680,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="6">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="I17" s="10">
         <f t="shared" ref="I17:I19" si="2">IF($D$9 = 0, 0, H17/$D$9)</f>
-        <v>4.8387096774193547E-2</v>
+        <v>4.6875E-2</v>
       </c>
       <c r="J17" s="11">
         <v>0.25</v>
@@ -850,7 +850,7 @@
       </c>
       <c r="I18" s="10">
         <f t="shared" si="2"/>
-        <v>0.30645161290322581</v>
+        <v>0.296875</v>
       </c>
       <c r="J18" s="11">
         <v>0.25</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="I19" s="10">
         <f t="shared" si="2"/>
-        <v>0.20967741935483872</v>
+        <v>0.203125</v>
       </c>
       <c r="J19" s="11">
         <v>0.25</v>
@@ -926,7 +926,7 @@
         <v>0.25</v>
       </c>
       <c r="H20" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I20" s="10">
         <v>0.25</v>
